--- a/data/nzd0542/nzd0542.xlsx
+++ b/data/nzd0542/nzd0542.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J548"/>
+  <dimension ref="A1:J551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20149,17 +20149,125 @@
         <v>285.59</v>
       </c>
       <c r="G548" t="n">
-        <v>292.3</v>
+        <v>283.21</v>
       </c>
       <c r="H548" t="n">
-        <v>306.75</v>
+        <v>290.6</v>
       </c>
       <c r="I548" t="n">
-        <v>323.13</v>
+        <v>303.51</v>
       </c>
       <c r="J548" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>298.74</v>
+      </c>
+      <c r="C549" t="n">
+        <v>287.12</v>
+      </c>
+      <c r="D549" t="n">
+        <v>281.03</v>
+      </c>
+      <c r="E549" t="n">
+        <v>266.9</v>
+      </c>
+      <c r="F549" t="n">
+        <v>284.56</v>
+      </c>
+      <c r="G549" t="n">
+        <v>282.18</v>
+      </c>
+      <c r="H549" t="n">
+        <v>290.6</v>
+      </c>
+      <c r="I549" t="n">
+        <v>303.51</v>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>296</v>
+      </c>
+      <c r="C550" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="D550" t="n">
+        <v>281.22</v>
+      </c>
+      <c r="E550" t="n">
+        <v>266.02</v>
+      </c>
+      <c r="F550" t="n">
+        <v>284.49</v>
+      </c>
+      <c r="G550" t="n">
+        <v>281.71</v>
+      </c>
+      <c r="H550" t="n">
+        <v>288.34</v>
+      </c>
+      <c r="I550" t="n">
+        <v>302.58</v>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>293.37</v>
+      </c>
+      <c r="C551" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="D551" t="n">
+        <v>279.86</v>
+      </c>
+      <c r="E551" t="n">
+        <v>265.79</v>
+      </c>
+      <c r="F551" t="n">
+        <v>282.8</v>
+      </c>
+      <c r="G551" t="n">
+        <v>280.22</v>
+      </c>
+      <c r="H551" t="n">
+        <v>286.53</v>
+      </c>
+      <c r="I551" t="n">
+        <v>300.38</v>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20174,7 +20282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25887,6 +25995,36 @@
       </c>
       <c r="B571" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -26055,28 +26193,28 @@
         <v>0.0309</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3468992249926696</v>
+        <v>-0.3456700476113362</v>
       </c>
       <c r="J2" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K2" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03869677295613105</v>
+        <v>0.03888117843201144</v>
       </c>
       <c r="M2" t="n">
-        <v>9.896340735636855</v>
+        <v>9.853962054582341</v>
       </c>
       <c r="N2" t="n">
-        <v>161.0764957162359</v>
+        <v>160.2290456773239</v>
       </c>
       <c r="O2" t="n">
-        <v>12.69159153598302</v>
+        <v>12.65816122812961</v>
       </c>
       <c r="P2" t="n">
-        <v>304.195465550554</v>
+        <v>304.1821895885351</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26133,28 +26271,28 @@
         <v>0.0262</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4113493505138829</v>
+        <v>-0.4075772459127477</v>
       </c>
       <c r="J3" t="n">
+        <v>550</v>
+      </c>
+      <c r="K3" t="n">
         <v>547</v>
       </c>
-      <c r="K3" t="n">
-        <v>544</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06957791867552732</v>
+        <v>0.06914480470715645</v>
       </c>
       <c r="M3" t="n">
-        <v>8.539618284114082</v>
+        <v>8.512040355144068</v>
       </c>
       <c r="N3" t="n">
-        <v>122.3018033067224</v>
+        <v>121.6940781101331</v>
       </c>
       <c r="O3" t="n">
-        <v>11.05901457213627</v>
+        <v>11.03150389158854</v>
       </c>
       <c r="P3" t="n">
-        <v>294.4856581136584</v>
+        <v>294.4448690166523</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26211,28 +26349,28 @@
         <v>0.0305</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3966278352263202</v>
+        <v>-0.3935364543109585</v>
       </c>
       <c r="J4" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K4" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1031654383570867</v>
+        <v>0.1027922365793543</v>
       </c>
       <c r="M4" t="n">
-        <v>6.702006491498765</v>
+        <v>6.680468529099215</v>
       </c>
       <c r="N4" t="n">
-        <v>74.16718382264622</v>
+        <v>73.80707617492196</v>
       </c>
       <c r="O4" t="n">
-        <v>8.6120371470777</v>
+        <v>8.591104479339194</v>
       </c>
       <c r="P4" t="n">
-        <v>288.4894408875891</v>
+        <v>288.4561341956841</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26289,28 +26427,28 @@
         <v>0.0369</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4072285111540739</v>
+        <v>-0.411908616290124</v>
       </c>
       <c r="J5" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K5" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1312335606165519</v>
+        <v>0.135089103690556</v>
       </c>
       <c r="M5" t="n">
-        <v>6.20473943594147</v>
+        <v>6.192695257690644</v>
       </c>
       <c r="N5" t="n">
-        <v>59.53903310237553</v>
+        <v>59.31276346558777</v>
       </c>
       <c r="O5" t="n">
-        <v>7.716154035682253</v>
+        <v>7.701478005265468</v>
       </c>
       <c r="P5" t="n">
-        <v>281.3868259849868</v>
+        <v>281.4372632105659</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26367,28 +26505,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4266536912099618</v>
+        <v>-0.4116035543567028</v>
       </c>
       <c r="J6" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K6" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1572661194875892</v>
+        <v>0.1471231406352348</v>
       </c>
       <c r="M6" t="n">
-        <v>5.787588461198336</v>
+        <v>5.822326394193513</v>
       </c>
       <c r="N6" t="n">
-        <v>52.90218368701065</v>
+        <v>53.6239663793605</v>
       </c>
       <c r="O6" t="n">
-        <v>7.273388734765292</v>
+        <v>7.322838683144707</v>
       </c>
       <c r="P6" t="n">
-        <v>281.6515955117083</v>
+        <v>281.4894286214428</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26445,28 +26583,28 @@
         <v>0.036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.41743216534571</v>
+        <v>-0.4105298366228929</v>
       </c>
       <c r="J7" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K7" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1411123539870038</v>
+        <v>0.1386660193708302</v>
       </c>
       <c r="M7" t="n">
-        <v>5.982036477855276</v>
+        <v>5.985530836385368</v>
       </c>
       <c r="N7" t="n">
-        <v>57.51888276449925</v>
+        <v>57.15922642432675</v>
       </c>
       <c r="O7" t="n">
-        <v>7.584120434466956</v>
+        <v>7.560372108853291</v>
       </c>
       <c r="P7" t="n">
-        <v>283.2223949556986</v>
+        <v>283.1479696869561</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26523,28 +26661,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4257720181876249</v>
+        <v>-0.4193448726927426</v>
       </c>
       <c r="J8" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K8" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1171545792765274</v>
+        <v>0.1160753262684849</v>
       </c>
       <c r="M8" t="n">
-        <v>6.632667453617723</v>
+        <v>6.625532329186937</v>
       </c>
       <c r="N8" t="n">
-        <v>73.60706396777783</v>
+        <v>72.64372450213044</v>
       </c>
       <c r="O8" t="n">
-        <v>8.579455924927748</v>
+        <v>8.523128797696915</v>
       </c>
       <c r="P8" t="n">
-        <v>288.6840172595116</v>
+        <v>288.6143716676588</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26601,28 +26739,28 @@
         <v>0.0421</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3708733088435605</v>
+        <v>-0.3681648054061544</v>
       </c>
       <c r="J9" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K9" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07273226860026627</v>
+        <v>0.07328532021129441</v>
       </c>
       <c r="M9" t="n">
-        <v>7.685984899312567</v>
+        <v>7.65662705742548</v>
       </c>
       <c r="N9" t="n">
-        <v>94.48634151499938</v>
+        <v>92.98088530391426</v>
       </c>
       <c r="O9" t="n">
-        <v>9.720408505561862</v>
+        <v>9.642659659238952</v>
       </c>
       <c r="P9" t="n">
-        <v>303.1012012571493</v>
+        <v>303.0717761892043</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26660,7 +26798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J548"/>
+  <dimension ref="A1:J551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55116,22 +55254,178 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>-46.49729509697497,169.7094302746211</t>
+          <t>-46.4972869119791,169.70931250376464</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>-46.497924901725135,169.70955304545203</t>
+          <t>-46.49791035974681,169.70934380216883</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>-46.49855643720219,169.7097008264293</t>
+          <t>-46.49853877097823,169.70944662199932</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-46.494216822895126,169.70983594144676</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-46.49482318882705,169.70962095247867</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-46.495434526737235,169.7094776049512</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-46.49603861789813,169.7092300911152</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-46.49667132712483,169.70939444245622</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>-46.497285984518726,169.70929915899475</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>-46.49791035974681,169.70934380216883</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>-46.49853877097823,169.70944662199932</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-46.49421435584463,169.70980044373482</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-46.494822900696796,169.7096168067158</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-46.49543469781778,169.70948006652492</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-46.496037825498796,169.709218690021</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-46.49667126409431,169.70939353554022</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-46.49728556130813,169.70929306963393</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-46.49790832473994,169.70931452107598</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>-46.49853793357446,169.70943457255873</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-46.49421198782601,169.70976637111707</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-46.494822900696796,169.7096168067158</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-46.495433473240034,169.70946244683967</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-46.49603761839423,169.70921571018965</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-46.49666974235553,169.70937163999713</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-46.49728421963838,169.70927376506523</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-46.49790669492817,169.70929107029113</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-46.49853595261429,169.7094060685074</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0542/nzd0542.xlsx
+++ b/data/nzd0542/nzd0542.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J551"/>
+  <dimension ref="A1:J554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20245,7 +20245,7 @@
         <v>293.37</v>
       </c>
       <c r="C551" t="n">
-        <v>286.8</v>
+        <v>283.6</v>
       </c>
       <c r="D551" t="n">
         <v>279.86</v>
@@ -20268,6 +20268,114 @@
       <c r="J551" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:49+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>292.38</v>
+      </c>
+      <c r="C552" t="n">
+        <v>282.57</v>
+      </c>
+      <c r="D552" t="n">
+        <v>279.09</v>
+      </c>
+      <c r="E552" t="n">
+        <v>265.81</v>
+      </c>
+      <c r="F552" t="n">
+        <v>281.68</v>
+      </c>
+      <c r="G552" t="n">
+        <v>278.77</v>
+      </c>
+      <c r="H552" t="n">
+        <v>284.45</v>
+      </c>
+      <c r="I552" t="n">
+        <v>298.53</v>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>290.45</v>
+      </c>
+      <c r="C553" t="n">
+        <v>281.83</v>
+      </c>
+      <c r="D553" t="n">
+        <v>278.47</v>
+      </c>
+      <c r="E553" t="n">
+        <v>265.57</v>
+      </c>
+      <c r="F553" t="n">
+        <v>280.58</v>
+      </c>
+      <c r="G553" t="n">
+        <v>277.32</v>
+      </c>
+      <c r="H553" t="n">
+        <v>281.21</v>
+      </c>
+      <c r="I553" t="n">
+        <v>295.31</v>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>290.18</v>
+      </c>
+      <c r="C554" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="D554" t="n">
+        <v>278.71</v>
+      </c>
+      <c r="E554" t="n">
+        <v>265.56</v>
+      </c>
+      <c r="F554" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="G554" t="n">
+        <v>277.35</v>
+      </c>
+      <c r="H554" t="n">
+        <v>280.84</v>
+      </c>
+      <c r="I554" t="n">
+        <v>294.95</v>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20282,7 +20390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B574"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26025,6 +26133,36 @@
       </c>
       <c r="B574" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -26193,28 +26331,28 @@
         <v>0.0309</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3456700476113362</v>
+        <v>-0.3499464881924368</v>
       </c>
       <c r="J2" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K2" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03888117843201144</v>
+        <v>0.04026420322617941</v>
       </c>
       <c r="M2" t="n">
-        <v>9.853962054582341</v>
+        <v>9.821124808912471</v>
       </c>
       <c r="N2" t="n">
-        <v>160.2290456773239</v>
+        <v>159.4437352258535</v>
       </c>
       <c r="O2" t="n">
-        <v>12.65816122812961</v>
+        <v>12.62710320009517</v>
       </c>
       <c r="P2" t="n">
-        <v>304.1821895885351</v>
+        <v>304.228805260913</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26271,28 +26409,28 @@
         <v>0.0262</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4075772459127477</v>
+        <v>-0.4103123921541234</v>
       </c>
       <c r="J3" t="n">
+        <v>553</v>
+      </c>
+      <c r="K3" t="n">
         <v>550</v>
       </c>
-      <c r="K3" t="n">
-        <v>547</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06914480470715645</v>
+        <v>0.07082162236122058</v>
       </c>
       <c r="M3" t="n">
-        <v>8.512040355144068</v>
+        <v>8.466976427182397</v>
       </c>
       <c r="N3" t="n">
-        <v>121.6940781101331</v>
+        <v>121.0222500806959</v>
       </c>
       <c r="O3" t="n">
-        <v>11.03150389158854</v>
+        <v>11.00101132081482</v>
       </c>
       <c r="P3" t="n">
-        <v>294.4448690166523</v>
+        <v>294.474581393394</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26349,28 +26487,28 @@
         <v>0.0305</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3935364543109585</v>
+        <v>-0.3925631854921399</v>
       </c>
       <c r="J4" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K4" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1027922365793543</v>
+        <v>0.103466028309445</v>
       </c>
       <c r="M4" t="n">
-        <v>6.680468529099215</v>
+        <v>6.648862294435705</v>
       </c>
       <c r="N4" t="n">
-        <v>73.80707617492196</v>
+        <v>73.4112364400896</v>
       </c>
       <c r="O4" t="n">
-        <v>8.591104479339194</v>
+        <v>8.56803573989334</v>
       </c>
       <c r="P4" t="n">
-        <v>288.4561341956841</v>
+        <v>288.4455750881687</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26427,28 +26565,28 @@
         <v>0.0369</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.411908616290124</v>
+        <v>-0.4170663778304323</v>
       </c>
       <c r="J5" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K5" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L5" t="n">
-        <v>0.135089103690556</v>
+        <v>0.1392531300368575</v>
       </c>
       <c r="M5" t="n">
-        <v>6.192695257690644</v>
+        <v>6.183061452956483</v>
       </c>
       <c r="N5" t="n">
-        <v>59.31276346558777</v>
+        <v>59.10922635954374</v>
       </c>
       <c r="O5" t="n">
-        <v>7.701478005265468</v>
+        <v>7.688252490621243</v>
       </c>
       <c r="P5" t="n">
-        <v>281.4372632105659</v>
+        <v>281.4932278579814</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26505,28 +26643,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4116035543567028</v>
+        <v>-0.4001313813440636</v>
       </c>
       <c r="J6" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K6" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1471231406352348</v>
+        <v>0.1403341523818904</v>
       </c>
       <c r="M6" t="n">
-        <v>5.822326394193513</v>
+        <v>5.842698313158611</v>
       </c>
       <c r="N6" t="n">
-        <v>53.6239663793605</v>
+        <v>53.91951199931145</v>
       </c>
       <c r="O6" t="n">
-        <v>7.322838683144707</v>
+        <v>7.342990671334905</v>
       </c>
       <c r="P6" t="n">
-        <v>281.4894286214428</v>
+        <v>281.3649571891148</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26583,28 +26721,28 @@
         <v>0.036</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4105298366228929</v>
+        <v>-0.4042799622819676</v>
       </c>
       <c r="J7" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K7" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1386660193708302</v>
+        <v>0.1361210008154147</v>
       </c>
       <c r="M7" t="n">
-        <v>5.985530836385368</v>
+        <v>5.985446265473546</v>
       </c>
       <c r="N7" t="n">
-        <v>57.15922642432675</v>
+        <v>57.02517731172719</v>
       </c>
       <c r="O7" t="n">
-        <v>7.560372108853291</v>
+        <v>7.551501659387171</v>
       </c>
       <c r="P7" t="n">
-        <v>283.1479696869561</v>
+        <v>283.0801625794455</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26661,28 +26799,28 @@
         <v>0.0362</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4193448726927426</v>
+        <v>-0.4140249575642828</v>
       </c>
       <c r="J8" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K8" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1160753262684849</v>
+        <v>0.1145333350346086</v>
       </c>
       <c r="M8" t="n">
-        <v>6.625532329186937</v>
+        <v>6.61338085656782</v>
       </c>
       <c r="N8" t="n">
-        <v>72.64372450213044</v>
+        <v>72.38772838709912</v>
       </c>
       <c r="O8" t="n">
-        <v>8.523128797696915</v>
+        <v>8.508097812501871</v>
       </c>
       <c r="P8" t="n">
-        <v>288.6143716676588</v>
+        <v>288.5564116155291</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26739,28 +26877,28 @@
         <v>0.0421</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3681648054061544</v>
+        <v>-0.3647572519814071</v>
       </c>
       <c r="J9" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="K9" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07328532021129441</v>
+        <v>0.07281379245866282</v>
       </c>
       <c r="M9" t="n">
-        <v>7.65662705742548</v>
+        <v>7.630909581833299</v>
       </c>
       <c r="N9" t="n">
-        <v>92.98088530391426</v>
+        <v>92.54069945147856</v>
       </c>
       <c r="O9" t="n">
-        <v>9.642659659238952</v>
+        <v>9.6198076618755</v>
       </c>
       <c r="P9" t="n">
-        <v>303.0717761892043</v>
+        <v>303.0346571951358</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26798,7 +26936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J551"/>
+  <dimension ref="A1:J554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55390,7 +55528,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>-46.494822900696796,169.7096168067158</t>
+          <t>-46.49482001938615,169.70957534908948</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -55426,6 +55564,162 @@
       <c r="J551" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:49+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-46.494211096439955,169.70975354530367</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-46.4948190919611,169.7095620049171</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-46.49543277991174,169.70945247098885</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-46.49603763640332,169.7092159693054</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-46.49666873386362,169.70935712934215</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-46.497282913983504,169.7092549787411</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-46.49790482198938,169.7092641213249</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-46.49853428680143,169.70938209919345</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-46.494209358683236,169.7097285414467</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-46.49481842565477,169.70955241784216</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-46.49543222164676,169.70944443848583</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-46.49603742029415,169.7092128599162</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-46.49666774337872,169.70934287780665</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-46.49728160832556,169.70923619241796</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-46.497901904514514,169.7092221431319</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-46.49853138737469,169.7093403796349</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-46.49420911557695,169.70972504349797</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-46.494818353621596,169.7095513814016</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-46.49543243774939,169.70944754784182</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-46.496037411289606,169.7092127303583</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-46.49666759030362,169.70934067529666</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-46.497281635339206,169.7092365811005</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-46.49790157134512,169.70921734932625</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-46.49853106321424,169.70933571533678</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
